--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0194.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0194.xlsx
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Ta nghĩ nó ở đằng kia.</t>
+          <t>Tao nghĩ nó ở đằng kia.</t>
         </is>
       </c>
     </row>
